--- a/Notes/datamapping-COLORS-31to255.xlsx
+++ b/Notes/datamapping-COLORS-31to255.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061DBC36-0242-4C49-9744-6AA2E767EBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AC287D-F4C9-46D8-9E6B-E8D297C3556E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A8B6DF86-6AB9-406B-88E7-6EC619762889}"/>
+    <workbookView xWindow="28695" yWindow="-870" windowWidth="14610" windowHeight="15585" xr2:uid="{A8B6DF86-6AB9-406B-88E7-6EC619762889}"/>
   </bookViews>
   <sheets>
     <sheet name="SilverMirror" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
   <si>
     <t>nite</t>
   </si>
@@ -173,7 +173,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="84">
+  <fills count="82">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,12 +206,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFBD7B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDEDEDE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -272,24 +266,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF940094"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC59463"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF42E631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFADADAD"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -314,12 +296,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A42F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF3A31C5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -398,18 +374,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFBD94"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF73A21"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF7BFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -669,6 +633,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF313A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3300"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2900"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF299410"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC642"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,58 +688,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="44" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="49" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="50" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -762,33 +750,31 @@
     <xf numFmtId="0" fontId="1" fillId="55" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="56" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="57" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="58" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="59" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="60" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="61" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="62" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="63" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="58" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="59" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="60" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="61" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="62" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="63" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="64" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="65" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="65" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="66" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="67" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="68" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="69" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="70" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="71" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="71" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="72" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="73" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="74" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="75" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="76" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="77" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="78" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="79" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="80" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="81" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="82" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="54" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="83" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,16 +783,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF313A4A"/>
-      <color rgb="FF29313A"/>
-      <color rgb="FF525A63"/>
-      <color rgb="FF842984"/>
-      <color rgb="FF7B217B"/>
-      <color rgb="FF7B317B"/>
-      <color rgb="FF733173"/>
-      <color rgb="FF6B316B"/>
-      <color rgb="FF848419"/>
-      <color rgb="FF844A00"/>
+      <color rgb="FFFFC642"/>
+      <color rgb="FF524AFF"/>
+      <color rgb="FF299410"/>
+      <color rgb="FFCD2900"/>
+      <color rgb="FFFFA563"/>
+      <color rgb="FFFF3300"/>
+      <color rgb="FF7331A5"/>
+      <color rgb="FF7B5219"/>
+      <color rgb="FF3ABD19"/>
+      <color rgb="FFFF3A08"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1183,184 +1169,184 @@
       </c>
     </row>
     <row r="2" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="37">
+      <c r="B2" s="33">
         <f>ROUND(((B3*255)/31),0)</f>
         <v>230</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="33">
         <f>ROUND(((C3*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="33">
         <f>ROUND(((D3*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="61">
         <f>ROUND(((F3*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="61">
         <f>ROUND(((G3*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="H2" s="4">
+        <v>165</v>
+      </c>
+      <c r="H2" s="61">
         <f>ROUND(((H3*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="J2" s="40">
+        <v>99</v>
+      </c>
+      <c r="J2" s="82">
         <f>ROUND(((J3*255)/31),0)</f>
-        <v>247</v>
-      </c>
-      <c r="K2" s="40">
+        <v>255</v>
+      </c>
+      <c r="K2" s="82">
         <f>ROUND(((K3*255)/31),0)</f>
-        <v>58</v>
-      </c>
-      <c r="L2" s="40">
+        <v>49</v>
+      </c>
+      <c r="L2" s="82">
         <f>ROUND(((L3*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="N2" s="18">
+        <v>0</v>
+      </c>
+      <c r="N2" s="16">
         <f>ROUND(((N3*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="O2" s="18">
+      <c r="O2" s="16">
         <f>ROUND(((O3*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="P2" s="18">
+      <c r="P2" s="16">
         <f>ROUND(((P3*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="42">
         <f>ROUND(((R3*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="S2" s="48">
+      <c r="S2" s="42">
         <f>ROUND(((S3*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="T2" s="48">
+      <c r="T2" s="42">
         <f>ROUND(((T3*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="V2" s="51">
+      <c r="V2" s="45">
         <f>ROUND(((V3*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W2" s="51">
+      <c r="W2" s="45">
         <f>ROUND(((W3*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="X2" s="51">
+      <c r="X2" s="45">
         <f>ROUND(((X3*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="Z2" s="58">
+      <c r="Z2" s="52">
         <f>ROUND(((Z3*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="AA2" s="58">
+      <c r="AA2" s="52">
         <f>ROUND(((AA3*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="AB2" s="58">
+      <c r="AB2" s="52">
         <f>ROUND(((AB3*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="AD2" s="63">
+      <c r="AD2" s="61">
         <f>ROUND(((AD3*255)/31),0)</f>
-        <v>107</v>
-      </c>
-      <c r="AE2" s="63">
+        <v>255</v>
+      </c>
+      <c r="AE2" s="61">
         <f>ROUND(((AE3*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="AF2" s="63">
+      <c r="AF2" s="61">
         <f>ROUND(((AF3*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
+        <v>99</v>
+      </c>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
     </row>
     <row r="3" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>28</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>31</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>16</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>31</v>
       </c>
-      <c r="G3" s="6">
-        <v>23</v>
-      </c>
-      <c r="H3" s="6">
-        <v>15</v>
+      <c r="G3" s="5">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5">
+        <v>12</v>
       </c>
       <c r="J3" s="1">
-        <v>30</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="6">
-        <v>2</v>
-      </c>
-      <c r="N3" s="6">
+        <v>31</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
         <v>24</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <v>18</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>12</v>
       </c>
       <c r="R3" s="1">
         <v>24</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="V3" s="6">
+      <c r="V3" s="5">
         <v>19</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="5">
         <v>14</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="6">
+      <c r="Z3" s="5">
         <v>18</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AA3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AD3" s="6">
-        <v>13</v>
-      </c>
-      <c r="AE3" s="6">
+      <c r="AD3" s="5">
+        <v>31</v>
+      </c>
+      <c r="AE3" s="5">
         <v>20</v>
       </c>
-      <c r="AF3" s="6">
-        <v>18</v>
-      </c>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
+      <c r="AF3" s="5">
+        <v>12</v>
+      </c>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
     </row>
     <row r="4" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -1377,169 +1363,184 @@
       </c>
     </row>
     <row r="5" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <f>ROUND(((B6*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <f>ROUND(((C6*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <f>ROUND(((D6*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="61">
         <f>ROUND(((F6*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="61">
         <f>ROUND(((G6*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="61">
         <f>ROUND(((H6*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="64">
         <f>ROUND(((J6*255)/31),0)</f>
+        <v>82</v>
+      </c>
+      <c r="K5" s="64">
+        <f>ROUND(((K6*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="K5" s="24">
-        <f>ROUND(((K6*255)/31),0)</f>
-        <v>66</v>
-      </c>
-      <c r="L5" s="24">
+      <c r="L5" s="64">
         <f>ROUND(((L6*255)/31),0)</f>
-        <v>247</v>
-      </c>
-      <c r="N5" s="18">
+        <v>255</v>
+      </c>
+      <c r="N5" s="16">
         <f>ROUND(((N6*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O5" s="16">
         <f>ROUND(((O6*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="P5" s="18">
+      <c r="P5" s="16">
         <f>ROUND(((P6*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="R5" s="25">
+      <c r="R5" s="21">
         <f>ROUND(((R6*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="21">
         <f>ROUND(((S6*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="T5" s="25">
+      <c r="T5" s="21">
         <f>ROUND(((T6*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="V5" s="51">
+      <c r="V5" s="45">
         <f>ROUND(((V6*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W5" s="51">
+      <c r="W5" s="45">
         <f>ROUND(((W6*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="X5" s="51">
+      <c r="X5" s="45">
         <f>ROUND(((X6*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="Z5" s="59">
+      <c r="Z5" s="53">
         <f>ROUND(((Z6*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="AA5" s="59">
+      <c r="AA5" s="53">
         <f>ROUND(((AA6*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="AB5" s="59">
+      <c r="AB5" s="53">
         <f>ROUND(((AB6*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="33"/>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="33"/>
+      <c r="AD5" s="83">
+        <f>ROUND(((AD6*255)/31),0)</f>
+        <v>206</v>
+      </c>
+      <c r="AE5" s="83">
+        <f>ROUND(((AE6*255)/31),0)</f>
+        <v>41</v>
+      </c>
+      <c r="AF5" s="83">
+        <f>ROUND(((AF6*255)/31),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
     </row>
     <row r="6" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>27</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>31</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>27</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>31</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>23</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>15</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="6" t="s">
+      <c r="J6" s="5">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5">
+        <v>9</v>
+      </c>
+      <c r="L6" s="1">
+        <v>31</v>
+      </c>
+      <c r="N6" s="5">
+        <v>24</v>
+      </c>
+      <c r="O6" s="5">
+        <v>18</v>
+      </c>
+      <c r="P6" s="5">
         <v>12</v>
       </c>
-      <c r="L6" s="1">
-        <v>30</v>
-      </c>
-      <c r="N6" s="6">
-        <v>24</v>
-      </c>
-      <c r="O6" s="6">
-        <v>18</v>
-      </c>
-      <c r="P6" s="6">
-        <v>12</v>
-      </c>
-      <c r="R6" s="6" t="s">
+      <c r="R6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="S6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="T6" s="1">
         <v>24</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6" s="5">
         <v>19</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="5">
         <v>14</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="X6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z6" s="6" t="s">
+      <c r="Z6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA6" s="6" t="s">
+      <c r="AA6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="5">
         <v>18</v>
       </c>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="6"/>
+      <c r="AD6" s="5">
+        <v>25</v>
+      </c>
+      <c r="AE6" s="5">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
     </row>
     <row r="7" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
@@ -1559,169 +1560,184 @@
       </c>
     </row>
     <row r="8" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="50">
+      <c r="B8" s="44">
         <f>ROUND(((B9*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="44">
         <f>ROUND(((C9*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="44">
         <f>ROUND(((D9*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="61">
         <f>ROUND(((F9*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="61">
         <f>ROUND(((G9*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="61">
         <f>ROUND(((H9*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="65">
         <f>ROUND(((J9*255)/31),0)</f>
-        <v>66</v>
-      </c>
-      <c r="K8" s="19">
+        <v>58</v>
+      </c>
+      <c r="K8" s="65">
         <f>ROUND(((K9*255)/31),0)</f>
-        <v>230</v>
-      </c>
-      <c r="L8" s="19">
+        <v>189</v>
+      </c>
+      <c r="L8" s="65">
         <f>ROUND(((L9*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="N8" s="18">
+        <v>25</v>
+      </c>
+      <c r="N8" s="16">
         <f>ROUND(((N9*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="16">
         <f>ROUND(((O9*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="P8" s="18">
+      <c r="P8" s="16">
         <f>ROUND(((P9*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="20">
         <f>ROUND(((R9*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="20">
         <f>ROUND(((S9*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="T8" s="23">
+      <c r="T8" s="20">
         <f>ROUND(((T9*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="V8" s="51">
+      <c r="V8" s="45">
         <f>ROUND(((V9*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W8" s="51">
+      <c r="W8" s="45">
         <f>ROUND(((W9*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="X8" s="51">
+      <c r="X8" s="45">
         <f>ROUND(((X9*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="Z8" s="60">
+      <c r="Z8" s="54">
         <f>ROUND(((Z9*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="AA8" s="60">
+      <c r="AA8" s="54">
         <f>ROUND(((AA9*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AB8" s="60">
+      <c r="AB8" s="54">
         <f>ROUND(((AB9*255)/31),0)</f>
         <v>25</v>
       </c>
-      <c r="AD8" s="33"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="33"/>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="33"/>
+      <c r="AD8" s="84">
+        <f>ROUND(((AD9*255)/31),0)</f>
+        <v>41</v>
+      </c>
+      <c r="AE8" s="84">
+        <f>ROUND(((AE9*255)/31),0)</f>
+        <v>148</v>
+      </c>
+      <c r="AF8" s="84">
+        <f>ROUND(((AF9*255)/31),0)</f>
+        <v>16</v>
+      </c>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
     </row>
     <row r="9" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>15</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>14</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>24</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>31</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>23</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>15</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5">
+        <v>7</v>
+      </c>
+      <c r="K9" s="1">
+        <v>23</v>
+      </c>
+      <c r="L9" s="5">
+        <v>3</v>
+      </c>
+      <c r="N9" s="5">
+        <v>24</v>
+      </c>
+      <c r="O9" s="5">
+        <v>18</v>
+      </c>
+      <c r="P9" s="5">
         <v>12</v>
       </c>
-      <c r="K9" s="1">
-        <v>28</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N9" s="6">
-        <v>24</v>
-      </c>
-      <c r="O9" s="6">
-        <v>18</v>
-      </c>
-      <c r="P9" s="6">
-        <v>12</v>
-      </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="S9" s="1">
         <v>21</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="5">
         <v>4</v>
       </c>
-      <c r="V9" s="6">
+      <c r="V9" s="5">
         <v>19</v>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="5">
         <v>14</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="X9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z9" s="6" t="s">
+      <c r="Z9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AA9" s="5">
         <v>15</v>
       </c>
-      <c r="AB9" s="6" t="s">
+      <c r="AB9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AJ9" s="6"/>
-      <c r="AL9" s="6"/>
-      <c r="AM9" s="6"/>
-      <c r="AN9" s="6"/>
+      <c r="AD9" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>18</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="5"/>
     </row>
     <row r="10" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
@@ -1741,114 +1757,123 @@
       </c>
     </row>
     <row r="11" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="38">
+      <c r="B11" s="34">
         <f>ROUND(((B12*255)/31),0)</f>
         <v>239</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="34">
         <f>ROUND(((C12*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="34">
         <f>ROUND(((D12*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="61">
         <f>ROUND(((F12*255)/31),0)</f>
         <v>239</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="61">
         <f>ROUND(((G12*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="61">
         <f>ROUND(((H12*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <f>ROUND(((J12*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <f>ROUND(((K12*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <f>ROUND(((L12*255)/31),0)</f>
         <v>25</v>
       </c>
-      <c r="N11" s="42">
+      <c r="N11" s="36">
         <f>ROUND(((N12*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="36">
         <f>ROUND(((O12*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="36">
         <f>ROUND(((P12*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="R11" s="22">
+      <c r="R11" s="19">
         <f>ROUND(((R12*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="S11" s="22">
+      <c r="S11" s="19">
         <f>ROUND(((S12*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="T11" s="22">
+      <c r="T11" s="19">
         <f>ROUND(((T12*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="V11" s="52">
+      <c r="V11" s="46">
         <f>ROUND(((V12*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="W11" s="52">
+      <c r="W11" s="46">
         <f>ROUND(((W12*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="X11" s="52">
+      <c r="X11" s="46">
         <f>ROUND(((X12*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="Z11" s="61">
+      <c r="Z11" s="55">
         <f>ROUND(((Z12*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="AA11" s="61">
+      <c r="AA11" s="55">
         <f>ROUND(((AA12*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="AB11" s="61">
+      <c r="AB11" s="55">
         <f>ROUND(((AB12*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="33"/>
-      <c r="AH11" s="33"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="33"/>
+      <c r="AD11" s="64">
+        <f>ROUND(((AD12*255)/31),0)</f>
+        <v>90</v>
+      </c>
+      <c r="AE11" s="64">
+        <f>ROUND(((AE12*255)/31),0)</f>
+        <v>82</v>
+      </c>
+      <c r="AF11" s="64">
+        <f>ROUND(((AF12*255)/31),0)</f>
+        <v>247</v>
+      </c>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
     </row>
     <row r="12" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>29</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>21</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>14</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>29</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>21</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>14</v>
       </c>
       <c r="J12" s="1">
@@ -1857,52 +1882,58 @@
       <c r="K12" s="1">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5">
+        <v>3</v>
+      </c>
+      <c r="N12" s="5">
+        <v>21</v>
+      </c>
+      <c r="O12" s="5">
         <v>16</v>
       </c>
-      <c r="N12" s="6">
-        <v>21</v>
-      </c>
-      <c r="O12" s="6">
-        <v>16</v>
-      </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="S12" s="6" t="s">
+      <c r="S12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="T12" s="6" t="s">
+      <c r="T12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="V12" s="6">
+      <c r="V12" s="5">
         <v>15</v>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="5">
         <v>12</v>
       </c>
-      <c r="X12" s="6" t="s">
+      <c r="X12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="Z12" s="6" t="s">
+      <c r="Z12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AA12" s="6" t="s">
+      <c r="AA12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB12" s="6" t="s">
+      <c r="AB12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AJ12" s="6"/>
-      <c r="AL12" s="6"/>
-      <c r="AM12" s="6"/>
-      <c r="AN12" s="6"/>
+      <c r="AD12" s="5">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>10</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>30</v>
+      </c>
+      <c r="AJ12" s="5"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="5"/>
     </row>
     <row r="13" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
@@ -1922,165 +1953,171 @@
       </c>
     </row>
     <row r="14" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="49">
+      <c r="B14" s="43">
         <f>ROUND(((B15*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="43">
         <f>ROUND(((C15*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="43">
         <f>ROUND(((D15*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="61">
         <f>ROUND(((F15*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="61">
         <f>ROUND(((G15*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="61">
         <f>ROUND(((H15*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="66">
         <f>ROUND(((J15*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="K14" s="17">
+        <v>115</v>
+      </c>
+      <c r="K14" s="66">
         <f>ROUND(((K15*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="17">
+        <v>49</v>
+      </c>
+      <c r="L14" s="66">
         <f>ROUND(((L15*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="N14" s="18">
+        <v>165</v>
+      </c>
+      <c r="N14" s="16">
         <f>ROUND(((N15*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="16">
         <f>ROUND(((O15*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="P14" s="18">
+      <c r="P14" s="16">
         <f>ROUND(((P15*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="R14" s="21">
+      <c r="R14" s="18">
         <f>ROUND(((R15*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="S14" s="21">
+      <c r="S14" s="18">
         <f>ROUND(((S15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="T14" s="21">
+      <c r="T14" s="18">
         <f>ROUND(((T15*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="V14" s="51">
+      <c r="V14" s="45">
         <f>ROUND(((V15*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W14" s="51">
+      <c r="W14" s="45">
         <f>ROUND(((W15*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="X14" s="51">
+      <c r="X14" s="45">
         <f>ROUND(((X15*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="Z14" s="62">
+      <c r="Z14" s="56">
         <f>ROUND(((Z15*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="AA14" s="62">
+      <c r="AA14" s="56">
         <f>ROUND(((AA15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="62">
+      <c r="AB14" s="56">
         <f>ROUND(((AB15*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="33"/>
-      <c r="AF14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="33"/>
+      <c r="AD14" s="85">
+        <v>255</v>
+      </c>
+      <c r="AE14" s="85">
+        <v>198</v>
+      </c>
+      <c r="AF14" s="85">
+        <v>66</v>
+      </c>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
     </row>
     <row r="15" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>31</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>23</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>15</v>
       </c>
       <c r="J15" s="1">
+        <v>14</v>
+      </c>
+      <c r="K15" s="5">
+        <v>6</v>
+      </c>
+      <c r="L15" s="1">
+        <v>20</v>
+      </c>
+      <c r="N15" s="5">
+        <v>24</v>
+      </c>
+      <c r="O15" s="5">
         <v>18</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="1">
-        <v>18</v>
-      </c>
-      <c r="N15" s="6">
-        <v>24</v>
-      </c>
-      <c r="O15" s="6">
-        <v>18</v>
-      </c>
-      <c r="P15" s="6">
+      <c r="P15" s="5">
         <v>12</v>
       </c>
       <c r="R15" s="1">
         <v>12</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="S15" s="5" t="s">
         <v>15</v>
       </c>
       <c r="T15" s="1">
         <v>12</v>
       </c>
-      <c r="V15" s="6">
+      <c r="V15" s="5">
         <v>19</v>
       </c>
-      <c r="W15" s="6">
+      <c r="W15" s="5">
         <v>14</v>
       </c>
-      <c r="X15" s="6" t="s">
+      <c r="X15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z15" s="6">
+      <c r="Z15" s="5">
         <v>10</v>
       </c>
-      <c r="AA15" s="6" t="s">
+      <c r="AA15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AB15" s="6">
+      <c r="AB15" s="5">
         <v>10</v>
       </c>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AI15" s="6"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AI15" s="5"/>
     </row>
     <row r="16" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F16" s="2" t="s">
@@ -2097,93 +2134,90 @@
       </c>
     </row>
     <row r="17" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F17" s="39">
+      <c r="F17" s="61">
         <f>ROUND(((F18*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="61">
         <f>ROUND(((G18*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="61">
         <f>ROUND(((H18*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <f>ROUND(((J18*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="8">
         <f>ROUND(((K18*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <f>ROUND(((L18*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="N17" s="43">
+      <c r="N17" s="37">
         <f>ROUND(((N18*255)/31),0)</f>
         <v>206</v>
       </c>
-      <c r="O17" s="43">
+      <c r="O17" s="37">
         <f>ROUND(((O18*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="P17" s="43">
+      <c r="P17" s="37">
         <f>ROUND(((P18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="R17" s="20">
+      <c r="R17" s="17">
         <f>ROUND(((R18*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="S17" s="20">
+      <c r="S17" s="17">
         <f>ROUND(((S18*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="T17" s="20">
+      <c r="T17" s="17">
         <f>ROUND(((T18*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="V17" s="53">
+      <c r="V17" s="47">
         <f>ROUND(((V18*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W17" s="53">
+      <c r="W17" s="47">
         <f>ROUND(((W18*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="X17" s="53">
+      <c r="X17" s="47">
         <f>ROUND(((X18*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="Z17" s="63">
+      <c r="Z17" s="57">
         <f>ROUND(((Z18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AA17" s="63">
+      <c r="AA17" s="57">
         <f>ROUND(((AA18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AB17" s="63">
+      <c r="AB17" s="57">
         <f>ROUND(((AB18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="33"/>
-      <c r="AF17" s="33"/>
-      <c r="AH17" s="33"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="33"/>
+      <c r="AH17" s="29"/>
+      <c r="AI17" s="29"/>
+      <c r="AJ17" s="29"/>
     </row>
     <row r="18" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>31</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>23</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>18</v>
       </c>
       <c r="J18" s="1">
@@ -2195,13 +2229,13 @@
       <c r="L18" s="1">
         <v>27</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="5">
         <v>25</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O18" s="5">
         <v>19</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="5">
         <v>15</v>
       </c>
       <c r="R18" s="1">
@@ -2213,27 +2247,27 @@
       <c r="T18" s="1">
         <v>21</v>
       </c>
-      <c r="V18" s="6">
+      <c r="V18" s="5">
         <v>19</v>
       </c>
-      <c r="W18" s="6">
+      <c r="W18" s="5">
         <v>14</v>
       </c>
-      <c r="X18" s="6">
+      <c r="X18" s="5">
         <v>11</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="Z18" s="5">
         <v>15</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AA18" s="5">
         <v>15</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AB18" s="5">
         <v>15</v>
       </c>
-      <c r="AD18" s="6"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
     </row>
     <row r="19" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F19" s="2" t="s">
@@ -2250,39 +2284,39 @@
       </c>
     </row>
     <row r="20" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <f>ROUND(((F21*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <f>ROUND(((G21*255)/31),0)</f>
         <v>206</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <f>ROUND(((H21*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <f>ROUND(((J21*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <f>ROUND(((K21*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <f>ROUND(((L21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="12">
         <f>ROUND(((N21*255)/31),0)</f>
         <v>66</v>
       </c>
-      <c r="O20" s="13">
+      <c r="O20" s="12">
         <f>ROUND(((O21*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="P20" s="13">
+      <c r="P20" s="12">
         <f>ROUND(((P21*255)/31),0)</f>
         <v>156</v>
       </c>
@@ -2298,66 +2332,63 @@
         <f>ROUND(((T21*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="V20" s="54">
+      <c r="V20" s="48">
         <f>ROUND(((V21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W20" s="54">
+      <c r="W20" s="48">
         <f>ROUND(((W21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="54">
+      <c r="X20" s="48">
         <f>ROUND(((X21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="54">
+      <c r="Z20" s="48">
         <f>ROUND(((Z21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="54">
+      <c r="AA20" s="48">
         <f>ROUND(((AA21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="54">
+      <c r="AB20" s="48">
         <f>ROUND(((AB21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="33"/>
-      <c r="AE20" s="33"/>
-      <c r="AF20" s="33"/>
-      <c r="AH20" s="33"/>
-      <c r="AI20" s="33"/>
-      <c r="AJ20" s="33"/>
+      <c r="AH20" s="29"/>
+      <c r="AI20" s="29"/>
+      <c r="AJ20" s="29"/>
     </row>
     <row r="21" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>12</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>25</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>2</v>
+      <c r="J21" s="5">
+        <v>5</v>
       </c>
       <c r="K21" s="1">
         <v>14</v>
       </c>
-      <c r="L21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="N21" s="6" t="s">
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="5">
         <v>13</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="5">
         <v>19</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="R21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="S21" s="1">
@@ -2366,28 +2397,28 @@
       <c r="T21" s="1">
         <v>13</v>
       </c>
-      <c r="V21" s="6" t="s">
+      <c r="V21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="W21" s="6" t="s">
+      <c r="W21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="6" t="s">
+      <c r="X21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Z21" s="6" t="s">
+      <c r="Z21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AA21" s="6" t="s">
+      <c r="AA21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AB21" s="6" t="s">
+      <c r="AB21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AD21" s="6"/>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AH21" s="6"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AH21" s="5"/>
     </row>
     <row r="22" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" s="2" t="s">
@@ -2404,93 +2435,90 @@
       </c>
     </row>
     <row r="23" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <f>ROUND(((F24*255)/31),0)</f>
         <v>247</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="6">
         <f>ROUND(((G24*255)/31),0)</f>
         <v>247</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <f>ROUND(((H24*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="7">
         <f>ROUND(((J24*255)/31),0)</f>
         <v>247</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <f>ROUND(((K24*255)/31),0)</f>
         <v>140</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="7">
         <f>ROUND(((L24*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="13">
         <f>ROUND(((N24*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="O23" s="14">
+      <c r="O23" s="13">
         <f>ROUND(((O24*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="P23" s="14">
+      <c r="P23" s="13">
         <f>ROUND(((P24*255)/31),0)</f>
         <v>25</v>
       </c>
-      <c r="R23" s="15">
+      <c r="R23" s="14">
         <f>ROUND(((R24*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="14">
         <f>ROUND(((S24*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="14">
         <f>ROUND(((T24*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="V23" s="55">
+      <c r="V23" s="49">
         <f>ROUND(((V24*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="W23" s="55">
+      <c r="W23" s="49">
         <f>ROUND(((W24*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="X23" s="55">
+      <c r="X23" s="49">
         <f>ROUND(((X24*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="Z23" s="64">
+      <c r="Z23" s="58">
         <f>ROUND(((Z24*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="AA23" s="64">
+      <c r="AA23" s="58">
         <f>ROUND(((AA24*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="AB23" s="64">
+      <c r="AB23" s="58">
         <f>ROUND(((AB24*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD23" s="33"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="33"/>
-      <c r="AH23" s="33"/>
-      <c r="AI23" s="33"/>
-      <c r="AJ23" s="33"/>
+      <c r="AH23" s="29"/>
+      <c r="AI23" s="29"/>
+      <c r="AJ23" s="29"/>
     </row>
     <row r="24" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>30</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>30</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J24" s="1">
@@ -2499,16 +2527,16 @@
       <c r="K24" s="1">
         <v>17</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="N24" s="6">
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
         <v>24</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O24" s="5">
         <v>24</v>
       </c>
-      <c r="P24" s="6" t="s">
+      <c r="P24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="R24" s="1">
@@ -2517,33 +2545,33 @@
       <c r="S24" s="1">
         <v>13</v>
       </c>
-      <c r="T24" s="6" t="s">
+      <c r="T24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="V24" s="6">
+      <c r="V24" s="5">
         <v>18</v>
       </c>
-      <c r="W24" s="6">
+      <c r="W24" s="5">
         <v>18</v>
       </c>
-      <c r="X24" s="6" t="s">
+      <c r="X24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="Z24" s="5">
         <v>18</v>
       </c>
-      <c r="AA24" s="6">
+      <c r="AA24" s="5">
         <v>10</v>
       </c>
-      <c r="AB24" s="6" t="s">
+      <c r="AB24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AH24" s="6"/>
-      <c r="AI24" s="6"/>
-      <c r="AJ24" s="6"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="5"/>
+      <c r="AJ24" s="5"/>
     </row>
     <row r="25" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F25" s="2" t="s">
@@ -2560,143 +2588,140 @@
       </c>
     </row>
     <row r="26" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <f>ROUND(((F27*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <f>ROUND(((G27*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <f>ROUND(((H27*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="J26" s="41">
+      <c r="J26" s="35">
         <f>ROUND(((J27*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="K26" s="41">
+      <c r="K26" s="35">
         <f>ROUND(((K27*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="L26" s="41">
+      <c r="L26" s="35">
         <f>ROUND(((L27*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="N26" s="44">
+      <c r="N26" s="38">
         <f>ROUND(((N27*255)/31),0)</f>
         <v>206</v>
       </c>
-      <c r="O26" s="44">
+      <c r="O26" s="38">
         <f>ROUND(((O27*255)/31),0)</f>
         <v>140</v>
       </c>
-      <c r="P26" s="44">
+      <c r="P26" s="38">
         <f>ROUND(((P27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="R26" s="47">
+      <c r="R26" s="41">
         <f>ROUND(((R27*255)/31),0)</f>
         <v>206</v>
       </c>
-      <c r="S26" s="47">
+      <c r="S26" s="41">
         <f>ROUND(((S27*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="T26" s="47">
+      <c r="T26" s="41">
         <f>ROUND(((T27*255)/31),0)</f>
         <v>206</v>
       </c>
-      <c r="V26" s="56">
+      <c r="V26" s="50">
         <f>ROUND(((V27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W26" s="56">
+      <c r="W26" s="50">
         <f>ROUND(((W27*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="X26" s="56">
+      <c r="X26" s="50">
         <f>ROUND(((X27*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="Z26" s="65">
+      <c r="Z26" s="59">
         <f>ROUND(((Z27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="AA26" s="65">
+      <c r="AA26" s="59">
         <f>ROUND(((AA27*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="AB26" s="65">
+      <c r="AB26" s="59">
         <f>ROUND(((AB27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
     </row>
     <row r="27" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>31</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>21</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>24</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="5">
         <v>31</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>15</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>31</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27" s="5">
         <v>25</v>
       </c>
-      <c r="O27" s="6">
+      <c r="O27" s="5">
         <v>17</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="5">
         <v>19</v>
       </c>
-      <c r="R27" s="6">
+      <c r="R27" s="5">
         <v>25</v>
       </c>
-      <c r="S27" s="6">
+      <c r="S27" s="5">
         <v>12</v>
       </c>
-      <c r="T27" s="6">
+      <c r="T27" s="5">
         <v>25</v>
       </c>
-      <c r="V27" s="6">
+      <c r="V27" s="5">
         <v>19</v>
       </c>
-      <c r="W27" s="6">
+      <c r="W27" s="5">
         <v>13</v>
       </c>
-      <c r="X27" s="6">
+      <c r="X27" s="5">
         <v>14</v>
       </c>
-      <c r="Z27" s="6">
+      <c r="Z27" s="5">
         <v>19</v>
       </c>
-      <c r="AA27" s="6" t="s">
+      <c r="AA27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AB27" s="6">
+      <c r="AB27" s="5">
         <v>19</v>
       </c>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
     </row>
     <row r="28" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="2" t="s">
@@ -2713,223 +2738,220 @@
       </c>
     </row>
     <row r="29" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F29" s="36">
+      <c r="F29" s="32">
         <f>ROUND(((F30*255)/31),0)</f>
         <v>181</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="32">
         <f>ROUND(((G30*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="32">
         <f>ROUND(((H30*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="31">
         <f>ROUND(((J30*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="31">
         <f>ROUND(((K30*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="31">
         <f>ROUND(((L30*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="N29" s="45">
+      <c r="N29" s="39">
         <f>ROUND(((N30*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O29" s="45">
+      <c r="O29" s="39">
         <f>ROUND(((O30*255)/31),0)</f>
         <v>140</v>
       </c>
-      <c r="P29" s="45">
+      <c r="P29" s="39">
         <f>ROUND(((P30*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="R29" s="46">
+      <c r="R29" s="40">
         <f>ROUND(((R30*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="S29" s="46">
+      <c r="S29" s="40">
         <f>ROUND(((S30*255)/31),0)</f>
         <v>66</v>
       </c>
-      <c r="T29" s="46">
+      <c r="T29" s="40">
         <f>ROUND(((T30*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="V29" s="57">
+      <c r="V29" s="51">
         <f>ROUND(((V30*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="W29" s="57">
+      <c r="W29" s="51">
         <f>ROUND(((W30*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="X29" s="57">
+      <c r="X29" s="51">
         <f>ROUND(((X30*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="Z29" s="66">
+      <c r="Z29" s="60">
         <f>ROUND(((Z30*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="AA29" s="66">
+      <c r="AA29" s="60">
         <f>ROUND(((AA30*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="AB29" s="66">
+      <c r="AB29" s="60">
         <f>ROUND(((AB30*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="AD29" s="33"/>
-      <c r="AE29" s="33"/>
-      <c r="AF29" s="33"/>
     </row>
     <row r="30" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F30" s="6">
+      <c r="F30" s="5">
         <v>22</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>23</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>24</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="5">
         <v>11</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>13</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>15</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="5">
         <v>16</v>
       </c>
-      <c r="O30" s="6">
+      <c r="O30" s="5">
         <v>17</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="5">
         <v>18</v>
       </c>
-      <c r="R30" s="6" t="s">
+      <c r="R30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="S30" s="6" t="s">
+      <c r="S30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="T30" s="6" t="s">
+      <c r="T30" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="V30" s="6">
+      <c r="V30" s="5">
         <v>10</v>
       </c>
-      <c r="W30" s="6">
+      <c r="W30" s="5">
         <v>11</v>
       </c>
-      <c r="X30" s="6">
+      <c r="X30" s="5">
         <v>12</v>
       </c>
-      <c r="Z30" s="6" t="s">
+      <c r="Z30" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA30" s="6" t="s">
+      <c r="AA30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AB30" s="6" t="s">
+      <c r="AB30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="6"/>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+      <c r="AF30" s="5"/>
+      <c r="AH30" s="5"/>
+      <c r="AI30" s="5"/>
+      <c r="AJ30" s="5"/>
     </row>
     <row r="31" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="32"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="33"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="29"/>
     </row>
     <row r="33" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
+      <c r="AD33" s="5"/>
+      <c r="AE33" s="5"/>
+      <c r="AF33" s="5"/>
+      <c r="AH33" s="5"/>
+      <c r="AI33" s="5"/>
+      <c r="AJ33" s="5"/>
     </row>
     <row r="34" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH34" s="34"/>
-      <c r="AI34" s="34"/>
-      <c r="AJ34" s="34"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
     </row>
     <row r="35" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
     </row>
     <row r="36" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
     </row>
     <row r="37" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2978,157 +3000,157 @@
       </c>
     </row>
     <row r="2" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="37">
+      <c r="B2" s="33">
         <f>ROUND(((B3*255)/31),0)</f>
         <v>230</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="33">
         <f>ROUND(((C3*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="33">
         <f>ROUND(((D3*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="F2" s="67">
+      <c r="F2" s="61">
         <f>ROUND(((F3*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G2" s="67">
+      <c r="G2" s="61">
         <f>ROUND(((G3*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="H2" s="67">
+      <c r="H2" s="61">
         <f>ROUND(((H3*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="J2" s="69">
+      <c r="J2" s="63">
         <f>ROUND(((J3*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="K2" s="69">
+      <c r="K2" s="63">
         <f>ROUND(((K3*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="L2" s="69">
+      <c r="L2" s="63">
         <f>ROUND(((L3*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="N2" s="76">
+      <c r="N2" s="70">
         <f>ROUND(((N3*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O2" s="76">
+      <c r="O2" s="70">
         <f>ROUND(((O3*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="70">
         <f>ROUND(((P3*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R2" s="77">
+      <c r="R2" s="71">
         <f>ROUND(((R3*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="S2" s="77">
+      <c r="S2" s="71">
         <f>ROUND(((S3*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="T2" s="77">
+      <c r="T2" s="71">
         <f>ROUND(((T3*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="V2" s="51">
+      <c r="V2" s="45">
         <f>ROUND(((V3*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W2" s="51">
+      <c r="W2" s="45">
         <f>ROUND(((W3*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X2" s="51">
+      <c r="X2" s="45">
         <f>ROUND(((X3*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="58">
+      <c r="Z2" s="52">
         <f>ROUND(((Z3*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA2" s="58">
+      <c r="AA2" s="52">
         <f>ROUND(((AA3*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB2" s="58">
+      <c r="AB2" s="52">
         <f>ROUND(((AB3*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
     </row>
     <row r="3" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>28</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>31</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>16</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>31</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>20</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>12</v>
       </c>
       <c r="J3" s="1">
         <v>31</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>7</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>1</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>16</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <v>11</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>9</v>
       </c>
       <c r="R3" s="1">
         <v>16</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S3" s="5">
         <v>4</v>
       </c>
-      <c r="T3" s="6">
+      <c r="T3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
     </row>
     <row r="4" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -3142,157 +3164,157 @@
       </c>
     </row>
     <row r="5" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <f>ROUND(((B6*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <f>ROUND(((C6*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <f>ROUND(((D6*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="F5" s="67">
+      <c r="F5" s="61">
         <f>ROUND(((F6*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G5" s="67">
+      <c r="G5" s="61">
         <f>ROUND(((G6*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="H5" s="67">
+      <c r="H5" s="61">
         <f>ROUND(((H6*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="J5" s="70">
+      <c r="J5" s="64">
         <f>ROUND(((J6*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="K5" s="70">
+      <c r="K5" s="64">
         <f>ROUND(((K6*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="L5" s="70">
+      <c r="L5" s="64">
         <f>ROUND(((L6*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="N5" s="76">
+      <c r="N5" s="70">
         <f>ROUND(((N6*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O5" s="76">
+      <c r="O5" s="70">
         <f>ROUND(((O6*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="70">
         <f>ROUND(((P6*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R5" s="78">
+      <c r="R5" s="72">
         <f>ROUND(((R6*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="S5" s="78">
+      <c r="S5" s="72">
         <f>ROUND(((S6*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="T5" s="78">
+      <c r="T5" s="72">
         <f>ROUND(((T6*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="V5" s="51">
+      <c r="V5" s="45">
         <f>ROUND(((V6*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W5" s="51">
+      <c r="W5" s="45">
         <f>ROUND(((W6*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X5" s="51">
+      <c r="X5" s="45">
         <f>ROUND(((X6*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="59">
+      <c r="Z5" s="53">
         <f>ROUND(((Z6*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="59">
+      <c r="AA5" s="53">
         <f>ROUND(((AA6*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB5" s="59">
+      <c r="AB5" s="53">
         <f>ROUND(((AB6*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="33"/>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="33"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
     </row>
     <row r="6" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>27</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>31</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>27</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>31</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>20</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>12</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>10</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>9</v>
       </c>
       <c r="L6" s="1">
         <v>31</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>16</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <v>11</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>9</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="5">
         <v>5</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <v>4</v>
       </c>
       <c r="T6" s="1">
         <v>16</v>
       </c>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="6"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
     </row>
     <row r="7" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
@@ -3306,157 +3328,157 @@
       </c>
     </row>
     <row r="8" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="50">
+      <c r="B8" s="44">
         <f>ROUND(((B9*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="44">
         <f>ROUND(((C9*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="44">
         <f>ROUND(((D9*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="61">
         <f>ROUND(((F9*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="61">
         <f>ROUND(((G9*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="61">
         <f>ROUND(((H9*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="65">
         <f>ROUND(((J9*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="65">
         <f>ROUND(((K9*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="65">
         <f>ROUND(((L9*255)/31),0)</f>
         <v>25</v>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="70">
         <f>ROUND(((N9*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="70">
         <f>ROUND(((O9*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="70">
         <f>ROUND(((P9*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="73">
         <f>ROUND(((R9*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="73">
         <f>ROUND(((S9*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="T8" s="79">
+      <c r="T8" s="73">
         <f>ROUND(((T9*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="V8" s="51">
+      <c r="V8" s="45">
         <f>ROUND(((V9*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W8" s="51">
+      <c r="W8" s="45">
         <f>ROUND(((W9*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X8" s="51">
+      <c r="X8" s="45">
         <f>ROUND(((X9*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="60">
+      <c r="Z8" s="54">
         <f>ROUND(((Z9*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="60">
+      <c r="AA8" s="54">
         <f>ROUND(((AA9*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="60">
+      <c r="AB8" s="54">
         <f>ROUND(((AB9*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD8" s="33"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="33"/>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="33"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="29"/>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
     </row>
     <row r="9" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>15</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>14</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>24</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>31</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>20</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>12</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>7</v>
       </c>
       <c r="K9" s="1">
         <v>23</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>3</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>16</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>11</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <v>9</v>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="5">
         <v>4</v>
       </c>
       <c r="S9" s="1">
         <v>12</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="5">
         <v>2</v>
       </c>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AJ9" s="6"/>
-      <c r="AL9" s="6"/>
-      <c r="AM9" s="6"/>
-      <c r="AN9" s="6"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="5"/>
     </row>
     <row r="10" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
@@ -3470,114 +3492,114 @@
       </c>
     </row>
     <row r="11" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="38">
+      <c r="B11" s="34">
         <f>ROUND(((B12*255)/31),0)</f>
         <v>239</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="34">
         <f>ROUND(((C12*255)/31),0)</f>
         <v>173</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="34">
         <f>ROUND(((D12*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="F11" s="68">
+      <c r="F11" s="62">
         <f>ROUND(((F12*255)/31),0)</f>
         <v>230</v>
       </c>
-      <c r="G11" s="68">
+      <c r="G11" s="62">
         <f>ROUND(((G12*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="H11" s="68">
+      <c r="H11" s="62">
         <f>ROUND(((H12*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <f>ROUND(((J12*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <f>ROUND(((K12*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <f>ROUND(((L12*255)/31),0)</f>
         <v>25</v>
       </c>
-      <c r="N11" s="76">
+      <c r="N11" s="70">
         <f>ROUND(((N12*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O11" s="76">
+      <c r="O11" s="70">
         <f>ROUND(((O12*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="70">
         <f>ROUND(((P12*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R11" s="80">
+      <c r="R11" s="74">
         <f>ROUND(((R12*255)/31),0)</f>
         <v>66</v>
       </c>
-      <c r="S11" s="80">
+      <c r="S11" s="74">
         <f>ROUND(((S12*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="T11" s="80">
+      <c r="T11" s="74">
         <f>ROUND(((T12*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="V11" s="52">
+      <c r="V11" s="46">
         <f>ROUND(((V12*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W11" s="52">
+      <c r="W11" s="46">
         <f>ROUND(((W12*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="52">
+      <c r="X11" s="46">
         <f>ROUND(((X12*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="61">
+      <c r="Z11" s="55">
         <f>ROUND(((Z12*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="61">
+      <c r="AA11" s="55">
         <f>ROUND(((AA12*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="61">
+      <c r="AB11" s="55">
         <f>ROUND(((AB12*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="33"/>
-      <c r="AH11" s="33"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="33"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
     </row>
     <row r="12" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>29</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>21</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>14</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>28</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>20</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>12</v>
       </c>
       <c r="J12" s="1">
@@ -3586,40 +3608,40 @@
       <c r="K12" s="1">
         <v>10</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>3</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <v>16</v>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="5">
         <v>11</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="5">
         <v>9</v>
       </c>
-      <c r="R12" s="6">
+      <c r="R12" s="5">
         <v>8</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="5">
         <v>5</v>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="5">
         <v>2</v>
       </c>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AJ12" s="6"/>
-      <c r="AL12" s="6"/>
-      <c r="AM12" s="6"/>
-      <c r="AN12" s="6"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="5"/>
     </row>
     <row r="13" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
@@ -3633,153 +3655,153 @@
       </c>
     </row>
     <row r="14" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="49">
+      <c r="B14" s="43">
         <f>ROUND(((B15*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="43">
         <f>ROUND(((C15*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="43">
         <f>ROUND(((D15*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="F14" s="67">
+      <c r="F14" s="61">
         <f>ROUND(((F15*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G14" s="67">
+      <c r="G14" s="61">
         <f>ROUND(((G15*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="H14" s="67">
+      <c r="H14" s="61">
         <f>ROUND(((H15*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="66">
         <f>ROUND(((J15*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="K14" s="72">
+      <c r="K14" s="66">
         <f>ROUND(((K15*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="L14" s="72">
+      <c r="L14" s="66">
         <f>ROUND(((L15*255)/31),0)</f>
         <v>165</v>
       </c>
-      <c r="N14" s="76">
+      <c r="N14" s="70">
         <f>ROUND(((N15*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O14" s="76">
+      <c r="O14" s="70">
         <f>ROUND(((O15*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="70">
         <f>ROUND(((P15*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R14" s="81">
+      <c r="R14" s="75">
         <f>ROUND(((R15*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="S14" s="81">
+      <c r="S14" s="75">
         <f>ROUND(((S15*255)/31),0)</f>
         <v>33</v>
       </c>
-      <c r="T14" s="81">
+      <c r="T14" s="75">
         <f>ROUND(((T15*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="V14" s="51">
+      <c r="V14" s="45">
         <f>ROUND(((V15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="51">
+      <c r="W14" s="45">
         <f>ROUND(((W15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="51">
+      <c r="X14" s="45">
         <f>ROUND(((X15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="62">
+      <c r="Z14" s="56">
         <f>ROUND(((Z15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="62">
+      <c r="AA14" s="56">
         <f>ROUND(((AA15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="62">
+      <c r="AB14" s="56">
         <f>ROUND(((AB15*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="33"/>
-      <c r="AF14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="33"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
     </row>
     <row r="15" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>1</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>1</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>31</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>20</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>12</v>
       </c>
       <c r="J15" s="1">
         <v>14</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>6</v>
       </c>
       <c r="L15" s="1">
         <v>20</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="5">
         <v>16</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="5">
         <v>11</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="5">
         <v>9</v>
       </c>
       <c r="R15" s="1">
         <v>9</v>
       </c>
-      <c r="S15" s="6">
+      <c r="S15" s="5">
         <v>4</v>
       </c>
       <c r="T15" s="1">
         <v>13</v>
       </c>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AI15" s="6"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AI15" s="5"/>
     </row>
     <row r="16" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F16" s="2" t="s">
@@ -3790,96 +3812,96 @@
       </c>
     </row>
     <row r="17" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F17" s="75">
+      <c r="F17" s="69">
         <f>ROUND(((F18*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="69">
         <f>ROUND(((G18*255)/31),0)</f>
         <v>181</v>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="69">
         <f>ROUND(((H18*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <f>ROUND(((J18*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="8">
         <f>ROUND(((K18*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <f>ROUND(((L18*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="N17" s="76">
+      <c r="N17" s="70">
         <f>ROUND(((N18*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O17" s="76">
+      <c r="O17" s="70">
         <f>ROUND(((O18*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P17" s="76">
+      <c r="P17" s="70">
         <f>ROUND(((P18*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R17" s="82">
+      <c r="R17" s="76">
         <f>ROUND(((R18*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="S17" s="82">
+      <c r="S17" s="76">
         <f>ROUND(((S18*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="T17" s="82">
+      <c r="T17" s="76">
         <f>ROUND(((T18*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="V17" s="53">
+      <c r="V17" s="47">
         <f>ROUND(((V18*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W17" s="53">
+      <c r="W17" s="47">
         <f>ROUND(((W18*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="X17" s="53">
+      <c r="X17" s="47">
         <f>ROUND(((X18*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="Z17" s="63">
+      <c r="Z17" s="57">
         <f>ROUND(((Z18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AA17" s="63">
+      <c r="AA17" s="57">
         <f>ROUND(((AA18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AB17" s="63">
+      <c r="AB17" s="57">
         <f>ROUND(((AB18*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="33"/>
-      <c r="AF17" s="33"/>
-      <c r="AH17" s="33"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="33"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="29"/>
+      <c r="AH17" s="29"/>
+      <c r="AI17" s="29"/>
+      <c r="AJ17" s="29"/>
     </row>
     <row r="18" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="F18" s="6">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="F18" s="5">
         <v>31</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>22</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>18</v>
       </c>
       <c r="J18" s="1">
@@ -3891,45 +3913,45 @@
       <c r="L18" s="1">
         <v>27</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="5">
         <v>16</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O18" s="5">
         <v>11</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="5">
         <v>9</v>
       </c>
       <c r="R18" s="1">
         <v>12</v>
       </c>
-      <c r="S18" s="6">
+      <c r="S18" s="5">
         <v>12</v>
       </c>
       <c r="T18" s="1">
         <v>12</v>
       </c>
-      <c r="V18" s="6">
+      <c r="V18" s="5">
         <v>19</v>
       </c>
-      <c r="W18" s="6">
+      <c r="W18" s="5">
         <v>14</v>
       </c>
-      <c r="X18" s="6">
+      <c r="X18" s="5">
         <v>11</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="Z18" s="5">
         <v>15</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AA18" s="5">
         <v>15</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AB18" s="5">
         <v>15</v>
       </c>
-      <c r="AD18" s="6"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
     </row>
     <row r="19" spans="2:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F19" s="2" t="s">
@@ -3958,39 +3980,39 @@
       </c>
     </row>
     <row r="20" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <f>ROUND(((F21*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <f>ROUND(((G21*255)/31),0)</f>
         <v>206</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <f>ROUND(((H21*255)/31),0)</f>
         <v>8</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <f>ROUND(((J21*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <f>ROUND(((K21*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <f>ROUND(((L21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="12">
         <f>ROUND(((N21*255)/31),0)</f>
         <v>66</v>
       </c>
-      <c r="O20" s="13">
+      <c r="O20" s="12">
         <f>ROUND(((O21*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="P20" s="13">
+      <c r="P20" s="12">
         <f>ROUND(((P21*255)/31),0)</f>
         <v>156</v>
       </c>
@@ -4006,66 +4028,66 @@
         <f>ROUND(((T21*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="V20" s="54">
+      <c r="V20" s="48">
         <f>ROUND(((V21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="W20" s="54">
+      <c r="W20" s="48">
         <f>ROUND(((W21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="54">
+      <c r="X20" s="48">
         <f>ROUND(((X21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="54">
+      <c r="Z20" s="48">
         <f>ROUND(((Z21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="54">
+      <c r="AA20" s="48">
         <f>ROUND(((AA21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="54">
+      <c r="AB20" s="48">
         <f>ROUND(((AB21*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="33"/>
-      <c r="AE20" s="33"/>
-      <c r="AF20" s="33"/>
-      <c r="AH20" s="33"/>
-      <c r="AI20" s="33"/>
-      <c r="AJ20" s="33"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AH20" s="29"/>
+      <c r="AI20" s="29"/>
+      <c r="AJ20" s="29"/>
     </row>
     <row r="21" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>12</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>25</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="5" t="s">
         <v>2</v>
       </c>
       <c r="K21" s="1">
         <v>14</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="N21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="5">
         <v>13</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="5">
         <v>19</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="R21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="S21" s="1">
@@ -4074,28 +4096,28 @@
       <c r="T21" s="1">
         <v>13</v>
       </c>
-      <c r="V21" s="6" t="s">
+      <c r="V21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="W21" s="6" t="s">
+      <c r="W21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="6" t="s">
+      <c r="X21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Z21" s="6" t="s">
+      <c r="Z21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AA21" s="6" t="s">
+      <c r="AA21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AB21" s="6" t="s">
+      <c r="AB21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AD21" s="6"/>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AH21" s="6"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AH21" s="5"/>
     </row>
     <row r="22" spans="2:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" s="2" t="s">
@@ -4106,96 +4128,96 @@
       </c>
     </row>
     <row r="23" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="73">
+      <c r="F23" s="67">
         <f>ROUND(((F24*255)/31),0)</f>
         <v>247</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G23" s="67">
         <f>ROUND(((G24*255)/31),0)</f>
         <v>247</v>
       </c>
-      <c r="H23" s="73">
+      <c r="H23" s="67">
         <f>ROUND(((H24*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="7">
         <f>ROUND(((J24*255)/31),0)</f>
         <v>247</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <f>ROUND(((K24*255)/31),0)</f>
         <v>140</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="7">
         <f>ROUND(((L24*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="84">
+      <c r="N23" s="78">
         <f>ROUND(((N24*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O23" s="84">
+      <c r="O23" s="78">
         <f>ROUND(((O24*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="P23" s="84">
+      <c r="P23" s="78">
         <f>ROUND(((P24*255)/31),0)</f>
         <v>25</v>
       </c>
-      <c r="R23" s="83">
+      <c r="R23" s="77">
         <f>ROUND(((R24*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="S23" s="83">
+      <c r="S23" s="77">
         <f>ROUND(((S24*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="T23" s="83">
+      <c r="T23" s="77">
         <f>ROUND(((T24*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="V23" s="55">
+      <c r="V23" s="49">
         <f>ROUND(((V24*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="W23" s="55">
+      <c r="W23" s="49">
         <f>ROUND(((W24*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="X23" s="55">
+      <c r="X23" s="49">
         <f>ROUND(((X24*255)/31),0)</f>
         <v>16</v>
       </c>
-      <c r="Z23" s="64">
+      <c r="Z23" s="58">
         <f>ROUND(((Z24*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="AA23" s="64">
+      <c r="AA23" s="58">
         <f>ROUND(((AA24*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="AB23" s="64">
+      <c r="AB23" s="58">
         <f>ROUND(((AB24*255)/31),0)</f>
         <v>0</v>
       </c>
-      <c r="AD23" s="33"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="33"/>
-      <c r="AH23" s="33"/>
-      <c r="AI23" s="33"/>
-      <c r="AJ23" s="33"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="AH23" s="29"/>
+      <c r="AI23" s="29"/>
+      <c r="AJ23" s="29"/>
     </row>
     <row r="24" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="F24" s="6">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="F24" s="5">
         <v>30</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>30</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>6</v>
       </c>
       <c r="J24" s="1">
@@ -4204,16 +4226,16 @@
       <c r="K24" s="1">
         <v>17</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="5">
         <v>16</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O24" s="5">
         <v>16</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="5">
         <v>3</v>
       </c>
       <c r="R24" s="1">
@@ -4222,33 +4244,33 @@
       <c r="S24" s="1">
         <v>9</v>
       </c>
-      <c r="T24" s="6">
-        <v>0</v>
-      </c>
-      <c r="V24" s="6">
+      <c r="T24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5">
         <v>18</v>
       </c>
-      <c r="W24" s="6">
+      <c r="W24" s="5">
         <v>18</v>
       </c>
-      <c r="X24" s="6" t="s">
+      <c r="X24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="Z24" s="5">
         <v>18</v>
       </c>
-      <c r="AA24" s="6">
+      <c r="AA24" s="5">
         <v>10</v>
       </c>
-      <c r="AB24" s="6" t="s">
+      <c r="AB24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AH24" s="6"/>
-      <c r="AI24" s="6"/>
-      <c r="AJ24" s="6"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="5"/>
+      <c r="AJ24" s="5"/>
     </row>
     <row r="25" spans="2:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F25" s="2" t="s">
@@ -4259,143 +4281,143 @@
       </c>
     </row>
     <row r="26" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F26" s="75">
+      <c r="F26" s="69">
         <f>ROUND(((F27*255)/31),0)</f>
         <v>255</v>
       </c>
-      <c r="G26" s="75">
+      <c r="G26" s="69">
         <f>ROUND(((G27*255)/31),0)</f>
         <v>181</v>
       </c>
-      <c r="H26" s="75">
+      <c r="H26" s="69">
         <f>ROUND(((H27*255)/31),0)</f>
         <v>148</v>
       </c>
-      <c r="J26" s="74">
+      <c r="J26" s="68">
         <f>ROUND(((J27*255)/31),0)</f>
         <v>222</v>
       </c>
-      <c r="K26" s="74">
+      <c r="K26" s="68">
         <f>ROUND(((K27*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="L26" s="74">
+      <c r="L26" s="68">
         <f>ROUND(((L27*255)/31),0)</f>
         <v>214</v>
       </c>
-      <c r="N26" s="76">
+      <c r="N26" s="70">
         <f>ROUND(((N27*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="O26" s="76">
+      <c r="O26" s="70">
         <f>ROUND(((O27*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P26" s="76">
+      <c r="P26" s="70">
         <f>ROUND(((P27*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="R26" s="85">
+      <c r="R26" s="79">
         <f>ROUND(((R27*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="S26" s="85">
+      <c r="S26" s="79">
         <f>ROUND(((S27*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="T26" s="85">
+      <c r="T26" s="79">
         <f>ROUND(((T27*255)/31),0)</f>
         <v>132</v>
       </c>
-      <c r="V26" s="56">
+      <c r="V26" s="50">
         <f>ROUND(((V27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="W26" s="56">
+      <c r="W26" s="50">
         <f>ROUND(((W27*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="X26" s="56">
+      <c r="X26" s="50">
         <f>ROUND(((X27*255)/31),0)</f>
         <v>115</v>
       </c>
-      <c r="Z26" s="65">
+      <c r="Z26" s="59">
         <f>ROUND(((Z27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="AA26" s="65">
+      <c r="AA26" s="59">
         <f>ROUND(((AA27*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="AB26" s="65">
+      <c r="AB26" s="59">
         <f>ROUND(((AB27*255)/31),0)</f>
         <v>156</v>
       </c>
-      <c r="AD26" s="33"/>
-      <c r="AE26" s="33"/>
-      <c r="AF26" s="33"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="29"/>
+      <c r="AF26" s="29"/>
     </row>
     <row r="27" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>31</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>22</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>18</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="5">
         <v>27</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>11</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>26</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27" s="5">
         <v>16</v>
       </c>
-      <c r="O27" s="6">
+      <c r="O27" s="5">
         <v>11</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="5">
         <v>9</v>
       </c>
-      <c r="R27" s="6">
+      <c r="R27" s="5">
         <v>16</v>
       </c>
-      <c r="S27" s="6">
+      <c r="S27" s="5">
         <v>5</v>
       </c>
-      <c r="T27" s="6">
+      <c r="T27" s="5">
         <v>16</v>
       </c>
-      <c r="V27" s="6">
+      <c r="V27" s="5">
         <v>19</v>
       </c>
-      <c r="W27" s="6">
+      <c r="W27" s="5">
         <v>13</v>
       </c>
-      <c r="X27" s="6">
+      <c r="X27" s="5">
         <v>14</v>
       </c>
-      <c r="Z27" s="6">
+      <c r="Z27" s="5">
         <v>19</v>
       </c>
-      <c r="AA27" s="6" t="s">
+      <c r="AA27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AB27" s="6">
+      <c r="AB27" s="5">
         <v>19</v>
       </c>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
     </row>
     <row r="28" spans="2:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="2" t="s">
@@ -4406,211 +4428,211 @@
       </c>
     </row>
     <row r="29" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F29" s="36">
+      <c r="F29" s="32">
         <f>ROUND(((F30*255)/31),0)</f>
         <v>181</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="32">
         <f>ROUND(((G30*255)/31),0)</f>
         <v>189</v>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="32">
         <f>ROUND(((H30*255)/31),0)</f>
         <v>197</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="31">
         <f>ROUND(((J30*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="31">
         <f>ROUND(((K30*255)/31),0)</f>
         <v>107</v>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="31">
         <f>ROUND(((L30*255)/31),0)</f>
         <v>123</v>
       </c>
-      <c r="N29" s="86">
+      <c r="N29" s="80">
         <f>ROUND(((N30*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="O29" s="86">
+      <c r="O29" s="80">
         <f>ROUND(((O30*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="P29" s="86">
+      <c r="P29" s="80">
         <f>ROUND(((P30*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="R29" s="87">
+      <c r="R29" s="81">
         <f>ROUND(((R30*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="S29" s="87">
+      <c r="S29" s="81">
         <f>ROUND(((S30*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="T29" s="87">
+      <c r="T29" s="81">
         <f>ROUND(((T30*255)/31),0)</f>
         <v>74</v>
       </c>
-      <c r="V29" s="57">
+      <c r="V29" s="51">
         <f>ROUND(((V30*255)/31),0)</f>
         <v>82</v>
       </c>
-      <c r="W29" s="57">
+      <c r="W29" s="51">
         <f>ROUND(((W30*255)/31),0)</f>
         <v>90</v>
       </c>
-      <c r="X29" s="57">
+      <c r="X29" s="51">
         <f>ROUND(((X30*255)/31),0)</f>
         <v>99</v>
       </c>
-      <c r="Z29" s="66">
+      <c r="Z29" s="60">
         <f>ROUND(((Z30*255)/31),0)</f>
         <v>41</v>
       </c>
-      <c r="AA29" s="66">
+      <c r="AA29" s="60">
         <f>ROUND(((AA30*255)/31),0)</f>
         <v>49</v>
       </c>
-      <c r="AB29" s="66">
+      <c r="AB29" s="60">
         <f>ROUND(((AB30*255)/31),0)</f>
         <v>58</v>
       </c>
-      <c r="AD29" s="33"/>
-      <c r="AE29" s="33"/>
-      <c r="AF29" s="33"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
     </row>
     <row r="30" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F30" s="6">
+      <c r="F30" s="5">
         <v>22</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>23</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>24</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="5">
         <v>11</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>13</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>15</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="5">
         <v>10</v>
       </c>
-      <c r="O30" s="6">
+      <c r="O30" s="5">
         <v>11</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="5">
         <v>12</v>
       </c>
-      <c r="R30" s="6">
+      <c r="R30" s="5">
         <v>6</v>
       </c>
-      <c r="S30" s="6">
+      <c r="S30" s="5">
         <v>7</v>
       </c>
-      <c r="T30" s="6">
+      <c r="T30" s="5">
         <v>9</v>
       </c>
-      <c r="V30" s="6">
+      <c r="V30" s="5">
         <v>10</v>
       </c>
-      <c r="W30" s="6">
+      <c r="W30" s="5">
         <v>11</v>
       </c>
-      <c r="X30" s="6">
+      <c r="X30" s="5">
         <v>12</v>
       </c>
-      <c r="Z30" s="6" t="s">
+      <c r="Z30" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA30" s="6" t="s">
+      <c r="AA30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AB30" s="6" t="s">
+      <c r="AB30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="6"/>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+      <c r="AF30" s="5"/>
+      <c r="AH30" s="5"/>
+      <c r="AI30" s="5"/>
+      <c r="AJ30" s="5"/>
     </row>
     <row r="31" spans="2:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="33"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="29"/>
     </row>
     <row r="33" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
+      <c r="AD33" s="5"/>
+      <c r="AE33" s="5"/>
+      <c r="AF33" s="5"/>
+      <c r="AH33" s="5"/>
+      <c r="AI33" s="5"/>
+      <c r="AJ33" s="5"/>
     </row>
     <row r="34" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH34" s="34"/>
-      <c r="AI34" s="34"/>
-      <c r="AJ34" s="34"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
     </row>
     <row r="35" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
     </row>
     <row r="36" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
     </row>
     <row r="37" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Notes/datamapping-COLORS-31to255.xlsx
+++ b/Notes/datamapping-COLORS-31to255.xlsx
@@ -1,40 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AC287D-F4C9-46D8-9E6B-E8D297C3556E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="28695" yWindow="-870" windowWidth="14610" windowHeight="15585" xr2:uid="{A8B6DF86-6AB9-406B-88E7-6EC619762889}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="SilverMirror" sheetId="2" r:id="rId1"/>
-    <sheet name="SourCrystal-ish" sheetId="4" r:id="rId2"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
@@ -173,7 +136,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="82">
+  <fills count="80">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,18 +608,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCD2900"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF299410"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC642"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -688,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -773,8 +724,6 @@
     <xf numFmtId="0" fontId="2" fillId="77" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="78" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="79" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="80" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="81" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -783,8 +732,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF524AFF"/>
       <color rgb="FFFFC642"/>
-      <color rgb="FF524AFF"/>
       <color rgb="FF299410"/>
       <color rgb="FFCD2900"/>
       <color rgb="FFFFA563"/>
@@ -1121,1843 +1070,6 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9ED113E-2A6C-4FC2-9B71-5DCD7F7B326C}">
-  <dimension ref="A1:AO38"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="6.7109375" style="1"/>
-    <col min="5" max="5" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6" max="8" width="6.7109375" style="1"/>
-    <col min="9" max="9" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10" max="12" width="6.7109375" style="1"/>
-    <col min="13" max="13" width="4.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16" width="6.7109375" style="1"/>
-    <col min="17" max="17" width="4.7109375" style="2" customWidth="1"/>
-    <col min="18" max="20" width="6.7109375" style="1"/>
-    <col min="21" max="21" width="6.7109375" style="2"/>
-    <col min="22" max="24" width="6.7109375" style="1"/>
-    <col min="25" max="25" width="6.7109375" style="2"/>
-    <col min="26" max="28" width="6.7109375" style="1"/>
-    <col min="29" max="29" width="6.7109375" style="2"/>
-    <col min="30" max="32" width="6.7109375" style="1"/>
-    <col min="33" max="33" width="6.7109375" style="2"/>
-    <col min="34" max="36" width="6.7109375" style="1"/>
-    <col min="37" max="37" width="6.7109375" style="2"/>
-    <col min="38" max="40" width="6.7109375" style="1"/>
-    <col min="41" max="41" width="6.7109375" style="2"/>
-    <col min="42" max="16384" width="6.7109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="33">
-        <f>ROUND(((B3*255)/31),0)</f>
-        <v>230</v>
-      </c>
-      <c r="C2" s="33">
-        <f>ROUND(((C3*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="D2" s="33">
-        <f>ROUND(((D3*255)/31),0)</f>
-        <v>132</v>
-      </c>
-      <c r="F2" s="61">
-        <f>ROUND(((F3*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="G2" s="61">
-        <f>ROUND(((G3*255)/31),0)</f>
-        <v>165</v>
-      </c>
-      <c r="H2" s="61">
-        <f>ROUND(((H3*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="J2" s="82">
-        <f>ROUND(((J3*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="K2" s="82">
-        <f>ROUND(((K3*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="L2" s="82">
-        <f>ROUND(((L3*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="16">
-        <f>ROUND(((N3*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="O2" s="16">
-        <f>ROUND(((O3*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="P2" s="16">
-        <f>ROUND(((P3*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="R2" s="42">
-        <f>ROUND(((R3*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="S2" s="42">
-        <f>ROUND(((S3*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="T2" s="42">
-        <f>ROUND(((T3*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="V2" s="45">
-        <f>ROUND(((V3*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="W2" s="45">
-        <f>ROUND(((W3*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="X2" s="45">
-        <f>ROUND(((X3*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="Z2" s="52">
-        <f>ROUND(((Z3*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="AA2" s="52">
-        <f>ROUND(((AA3*255)/31),0)</f>
-        <v>33</v>
-      </c>
-      <c r="AB2" s="52">
-        <f>ROUND(((AB3*255)/31),0)</f>
-        <v>8</v>
-      </c>
-      <c r="AD2" s="61">
-        <f>ROUND(((AD3*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="AE2" s="61">
-        <f>ROUND(((AE3*255)/31),0)</f>
-        <v>165</v>
-      </c>
-      <c r="AF2" s="61">
-        <f>ROUND(((AF3*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-    </row>
-    <row r="3" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="5">
-        <v>28</v>
-      </c>
-      <c r="C3" s="5">
-        <v>31</v>
-      </c>
-      <c r="D3" s="5">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5">
-        <v>31</v>
-      </c>
-      <c r="G3" s="5">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5">
-        <v>12</v>
-      </c>
-      <c r="J3" s="1">
-        <v>31</v>
-      </c>
-      <c r="K3" s="5">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>24</v>
-      </c>
-      <c r="O3" s="5">
-        <v>18</v>
-      </c>
-      <c r="P3" s="5">
-        <v>12</v>
-      </c>
-      <c r="R3" s="1">
-        <v>24</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="V3" s="5">
-        <v>19</v>
-      </c>
-      <c r="W3" s="5">
-        <v>14</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>18</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>31</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>20</v>
-      </c>
-      <c r="AF3" s="5">
-        <v>12</v>
-      </c>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="5"/>
-      <c r="AL3" s="5"/>
-      <c r="AM3" s="5"/>
-      <c r="AN3" s="5"/>
-    </row>
-    <row r="4" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="15">
-        <f>ROUND(((B6*255)/31),0)</f>
-        <v>222</v>
-      </c>
-      <c r="C5" s="15">
-        <f>ROUND(((C6*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="D5" s="15">
-        <f>ROUND(((D6*255)/31),0)</f>
-        <v>222</v>
-      </c>
-      <c r="F5" s="61">
-        <f>ROUND(((F6*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="G5" s="61">
-        <f>ROUND(((G6*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="H5" s="61">
-        <f>ROUND(((H6*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="J5" s="64">
-        <f>ROUND(((J6*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="K5" s="64">
-        <f>ROUND(((K6*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="L5" s="64">
-        <f>ROUND(((L6*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="N5" s="16">
-        <f>ROUND(((N6*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="O5" s="16">
-        <f>ROUND(((O6*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="P5" s="16">
-        <f>ROUND(((P6*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="R5" s="21">
-        <f>ROUND(((R6*255)/31),0)</f>
-        <v>58</v>
-      </c>
-      <c r="S5" s="21">
-        <f>ROUND(((S6*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="T5" s="21">
-        <f>ROUND(((T6*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="V5" s="45">
-        <f>ROUND(((V6*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="W5" s="45">
-        <f>ROUND(((W6*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="X5" s="45">
-        <f>ROUND(((X6*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="Z5" s="53">
-        <f>ROUND(((Z6*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="AA5" s="53">
-        <f>ROUND(((AA6*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="AB5" s="53">
-        <f>ROUND(((AB6*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="AD5" s="83">
-        <f>ROUND(((AD6*255)/31),0)</f>
-        <v>206</v>
-      </c>
-      <c r="AE5" s="83">
-        <f>ROUND(((AE6*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="AF5" s="83">
-        <f>ROUND(((AF6*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-    </row>
-    <row r="6" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
-        <v>27</v>
-      </c>
-      <c r="C6" s="5">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5">
-        <v>27</v>
-      </c>
-      <c r="F6" s="5">
-        <v>31</v>
-      </c>
-      <c r="G6" s="5">
-        <v>23</v>
-      </c>
-      <c r="H6" s="5">
-        <v>15</v>
-      </c>
-      <c r="J6" s="5">
-        <v>10</v>
-      </c>
-      <c r="K6" s="5">
-        <v>9</v>
-      </c>
-      <c r="L6" s="1">
-        <v>31</v>
-      </c>
-      <c r="N6" s="5">
-        <v>24</v>
-      </c>
-      <c r="O6" s="5">
-        <v>18</v>
-      </c>
-      <c r="P6" s="5">
-        <v>12</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="T6" s="1">
-        <v>24</v>
-      </c>
-      <c r="V6" s="5">
-        <v>19</v>
-      </c>
-      <c r="W6" s="5">
-        <v>14</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB6" s="5">
-        <v>18</v>
-      </c>
-      <c r="AD6" s="5">
-        <v>25</v>
-      </c>
-      <c r="AE6" s="5">
-        <v>5</v>
-      </c>
-      <c r="AF6" s="5">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="5"/>
-      <c r="AI6" s="5"/>
-      <c r="AL6" s="5"/>
-      <c r="AM6" s="5"/>
-      <c r="AN6" s="5"/>
-    </row>
-    <row r="7" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="44">
-        <f>ROUND(((B9*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="C8" s="44">
-        <f>ROUND(((C9*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="D8" s="44">
-        <f>ROUND(((D9*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="F8" s="61">
-        <f>ROUND(((F9*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="G8" s="61">
-        <f>ROUND(((G9*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="H8" s="61">
-        <f>ROUND(((H9*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="J8" s="65">
-        <f>ROUND(((J9*255)/31),0)</f>
-        <v>58</v>
-      </c>
-      <c r="K8" s="65">
-        <f>ROUND(((K9*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="L8" s="65">
-        <f>ROUND(((L9*255)/31),0)</f>
-        <v>25</v>
-      </c>
-      <c r="N8" s="16">
-        <f>ROUND(((N9*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="O8" s="16">
-        <f>ROUND(((O9*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="P8" s="16">
-        <f>ROUND(((P9*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="R8" s="20">
-        <f>ROUND(((R9*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="S8" s="20">
-        <f>ROUND(((S9*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="T8" s="20">
-        <f>ROUND(((T9*255)/31),0)</f>
-        <v>33</v>
-      </c>
-      <c r="V8" s="45">
-        <f>ROUND(((V9*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="W8" s="45">
-        <f>ROUND(((W9*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="X8" s="45">
-        <f>ROUND(((X9*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="Z8" s="54">
-        <f>ROUND(((Z9*255)/31),0)</f>
-        <v>33</v>
-      </c>
-      <c r="AA8" s="54">
-        <f>ROUND(((AA9*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="AB8" s="54">
-        <f>ROUND(((AB9*255)/31),0)</f>
-        <v>25</v>
-      </c>
-      <c r="AD8" s="84">
-        <f>ROUND(((AD9*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="AE8" s="84">
-        <f>ROUND(((AE9*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="AF8" s="84">
-        <f>ROUND(((AF9*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="29"/>
-      <c r="AJ8" s="29"/>
-    </row>
-    <row r="9" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="5">
-        <v>15</v>
-      </c>
-      <c r="C9" s="5">
-        <v>14</v>
-      </c>
-      <c r="D9" s="5">
-        <v>24</v>
-      </c>
-      <c r="F9" s="5">
-        <v>31</v>
-      </c>
-      <c r="G9" s="5">
-        <v>23</v>
-      </c>
-      <c r="H9" s="5">
-        <v>15</v>
-      </c>
-      <c r="J9" s="5">
-        <v>7</v>
-      </c>
-      <c r="K9" s="1">
-        <v>23</v>
-      </c>
-      <c r="L9" s="5">
-        <v>3</v>
-      </c>
-      <c r="N9" s="5">
-        <v>24</v>
-      </c>
-      <c r="O9" s="5">
-        <v>18</v>
-      </c>
-      <c r="P9" s="5">
-        <v>12</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" s="1">
-        <v>21</v>
-      </c>
-      <c r="T9" s="5">
-        <v>4</v>
-      </c>
-      <c r="V9" s="5">
-        <v>19</v>
-      </c>
-      <c r="W9" s="5">
-        <v>14</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA9" s="5">
-        <v>15</v>
-      </c>
-      <c r="AB9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD9" s="5">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="5">
-        <v>18</v>
-      </c>
-      <c r="AF9" s="5">
-        <v>2</v>
-      </c>
-      <c r="AH9" s="5"/>
-      <c r="AJ9" s="5"/>
-      <c r="AL9" s="5"/>
-      <c r="AM9" s="5"/>
-      <c r="AN9" s="5"/>
-    </row>
-    <row r="10" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="34">
-        <f>ROUND(((B12*255)/31),0)</f>
-        <v>239</v>
-      </c>
-      <c r="C11" s="34">
-        <f>ROUND(((C12*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="D11" s="34">
-        <f>ROUND(((D12*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="F11" s="61">
-        <f>ROUND(((F12*255)/31),0)</f>
-        <v>239</v>
-      </c>
-      <c r="G11" s="61">
-        <f>ROUND(((G12*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="H11" s="61">
-        <f>ROUND(((H12*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="J11" s="11">
-        <f>ROUND(((J12*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="K11" s="11">
-        <f>ROUND(((K12*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="L11" s="11">
-        <f>ROUND(((L12*255)/31),0)</f>
-        <v>25</v>
-      </c>
-      <c r="N11" s="36">
-        <f>ROUND(((N12*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="O11" s="36">
-        <f>ROUND(((O12*255)/31),0)</f>
-        <v>132</v>
-      </c>
-      <c r="P11" s="36">
-        <f>ROUND(((P12*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="R11" s="19">
-        <f>ROUND(((R12*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="S11" s="19">
-        <f>ROUND(((S12*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="T11" s="19">
-        <f>ROUND(((T12*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="V11" s="46">
-        <f>ROUND(((V12*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="W11" s="46">
-        <f>ROUND(((W12*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="X11" s="46">
-        <f>ROUND(((X12*255)/31),0)</f>
-        <v>8</v>
-      </c>
-      <c r="Z11" s="55">
-        <f>ROUND(((Z12*255)/31),0)</f>
-        <v>58</v>
-      </c>
-      <c r="AA11" s="55">
-        <f>ROUND(((AA12*255)/31),0)</f>
-        <v>33</v>
-      </c>
-      <c r="AB11" s="55">
-        <f>ROUND(((AB12*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="AD11" s="64">
-        <f>ROUND(((AD12*255)/31),0)</f>
-        <v>90</v>
-      </c>
-      <c r="AE11" s="64">
-        <f>ROUND(((AE12*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="AF11" s="64">
-        <f>ROUND(((AF12*255)/31),0)</f>
-        <v>247</v>
-      </c>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="29"/>
-      <c r="AJ11" s="29"/>
-    </row>
-    <row r="12" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="5">
-        <v>29</v>
-      </c>
-      <c r="C12" s="5">
-        <v>21</v>
-      </c>
-      <c r="D12" s="5">
-        <v>14</v>
-      </c>
-      <c r="F12" s="5">
-        <v>29</v>
-      </c>
-      <c r="G12" s="5">
-        <v>21</v>
-      </c>
-      <c r="H12" s="5">
-        <v>14</v>
-      </c>
-      <c r="J12" s="1">
-        <v>15</v>
-      </c>
-      <c r="K12" s="1">
-        <v>10</v>
-      </c>
-      <c r="L12" s="5">
-        <v>3</v>
-      </c>
-      <c r="N12" s="5">
-        <v>21</v>
-      </c>
-      <c r="O12" s="5">
-        <v>16</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="V12" s="5">
-        <v>15</v>
-      </c>
-      <c r="W12" s="5">
-        <v>12</v>
-      </c>
-      <c r="X12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD12" s="5">
-        <v>11</v>
-      </c>
-      <c r="AE12" s="5">
-        <v>10</v>
-      </c>
-      <c r="AF12" s="5">
-        <v>30</v>
-      </c>
-      <c r="AJ12" s="5"/>
-      <c r="AL12" s="5"/>
-      <c r="AM12" s="5"/>
-      <c r="AN12" s="5"/>
-    </row>
-    <row r="13" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="43">
-        <f>ROUND(((B15*255)/31),0)</f>
-        <v>8</v>
-      </c>
-      <c r="C14" s="43">
-        <f>ROUND(((C15*255)/31),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D14" s="43">
-        <f>ROUND(((D15*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="F14" s="61">
-        <f>ROUND(((F15*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="G14" s="61">
-        <f>ROUND(((G15*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="H14" s="61">
-        <f>ROUND(((H15*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="J14" s="66">
-        <f>ROUND(((J15*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="K14" s="66">
-        <f>ROUND(((K15*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="L14" s="66">
-        <f>ROUND(((L15*255)/31),0)</f>
-        <v>165</v>
-      </c>
-      <c r="N14" s="16">
-        <f>ROUND(((N15*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="O14" s="16">
-        <f>ROUND(((O15*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="P14" s="16">
-        <f>ROUND(((P15*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="R14" s="18">
-        <f>ROUND(((R15*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="S14" s="18">
-        <f>ROUND(((S15*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T14" s="18">
-        <f>ROUND(((T15*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="V14" s="45">
-        <f>ROUND(((V15*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="W14" s="45">
-        <f>ROUND(((W15*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="X14" s="45">
-        <f>ROUND(((X15*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="Z14" s="56">
-        <f>ROUND(((Z15*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="AA14" s="56">
-        <f>ROUND(((AA15*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AB14" s="56">
-        <f>ROUND(((AB15*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="AD14" s="85">
-        <v>255</v>
-      </c>
-      <c r="AE14" s="85">
-        <v>198</v>
-      </c>
-      <c r="AF14" s="85">
-        <v>66</v>
-      </c>
-      <c r="AH14" s="29"/>
-      <c r="AI14" s="29"/>
-      <c r="AJ14" s="29"/>
-    </row>
-    <row r="15" spans="2:40" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="5">
-        <v>31</v>
-      </c>
-      <c r="G15" s="5">
-        <v>23</v>
-      </c>
-      <c r="H15" s="5">
-        <v>15</v>
-      </c>
-      <c r="J15" s="1">
-        <v>14</v>
-      </c>
-      <c r="K15" s="5">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <v>20</v>
-      </c>
-      <c r="N15" s="5">
-        <v>24</v>
-      </c>
-      <c r="O15" s="5">
-        <v>18</v>
-      </c>
-      <c r="P15" s="5">
-        <v>12</v>
-      </c>
-      <c r="R15" s="1">
-        <v>12</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="T15" s="1">
-        <v>12</v>
-      </c>
-      <c r="V15" s="5">
-        <v>19</v>
-      </c>
-      <c r="W15" s="5">
-        <v>14</v>
-      </c>
-      <c r="X15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>10</v>
-      </c>
-      <c r="AA15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="5"/>
-      <c r="AE15" s="5"/>
-      <c r="AF15" s="5"/>
-      <c r="AI15" s="5"/>
-    </row>
-    <row r="16" spans="2:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F17" s="61">
-        <f>ROUND(((F18*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="G17" s="61">
-        <f>ROUND(((G18*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="H17" s="61">
-        <f>ROUND(((H18*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="J17" s="8">
-        <f>ROUND(((J18*255)/31),0)</f>
-        <v>222</v>
-      </c>
-      <c r="K17" s="8">
-        <f>ROUND(((K18*255)/31),0)</f>
-        <v>222</v>
-      </c>
-      <c r="L17" s="8">
-        <f>ROUND(((L18*255)/31),0)</f>
-        <v>222</v>
-      </c>
-      <c r="N17" s="37">
-        <f>ROUND(((N18*255)/31),0)</f>
-        <v>206</v>
-      </c>
-      <c r="O17" s="37">
-        <f>ROUND(((O18*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="P17" s="37">
-        <f>ROUND(((P18*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="R17" s="17">
-        <f>ROUND(((R18*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="S17" s="17">
-        <f>ROUND(((S18*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="T17" s="17">
-        <f>ROUND(((T18*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="V17" s="47">
-        <f>ROUND(((V18*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="W17" s="47">
-        <f>ROUND(((W18*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="X17" s="47">
-        <f>ROUND(((X18*255)/31),0)</f>
-        <v>90</v>
-      </c>
-      <c r="Z17" s="57">
-        <f>ROUND(((Z18*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="AA17" s="57">
-        <f>ROUND(((AA18*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="AB17" s="57">
-        <f>ROUND(((AB18*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="AH17" s="29"/>
-      <c r="AI17" s="29"/>
-      <c r="AJ17" s="29"/>
-    </row>
-    <row r="18" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F18" s="5">
-        <v>31</v>
-      </c>
-      <c r="G18" s="5">
-        <v>23</v>
-      </c>
-      <c r="H18" s="5">
-        <v>18</v>
-      </c>
-      <c r="J18" s="1">
-        <v>27</v>
-      </c>
-      <c r="K18" s="1">
-        <v>27</v>
-      </c>
-      <c r="L18" s="1">
-        <v>27</v>
-      </c>
-      <c r="N18" s="5">
-        <v>25</v>
-      </c>
-      <c r="O18" s="5">
-        <v>19</v>
-      </c>
-      <c r="P18" s="5">
-        <v>15</v>
-      </c>
-      <c r="R18" s="1">
-        <v>21</v>
-      </c>
-      <c r="S18" s="1">
-        <v>21</v>
-      </c>
-      <c r="T18" s="1">
-        <v>21</v>
-      </c>
-      <c r="V18" s="5">
-        <v>19</v>
-      </c>
-      <c r="W18" s="5">
-        <v>14</v>
-      </c>
-      <c r="X18" s="5">
-        <v>11</v>
-      </c>
-      <c r="Z18" s="5">
-        <v>15</v>
-      </c>
-      <c r="AA18" s="5">
-        <v>15</v>
-      </c>
-      <c r="AB18" s="5">
-        <v>15</v>
-      </c>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="5"/>
-    </row>
-    <row r="19" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="9">
-        <f>ROUND(((F21*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="G20" s="9">
-        <f>ROUND(((G21*255)/31),0)</f>
-        <v>206</v>
-      </c>
-      <c r="H20" s="9">
-        <f>ROUND(((H21*255)/31),0)</f>
-        <v>8</v>
-      </c>
-      <c r="J20" s="10">
-        <f>ROUND(((J21*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="K20" s="10">
-        <f>ROUND(((K21*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="L20" s="10">
-        <f>ROUND(((L21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="12">
-        <f>ROUND(((N21*255)/31),0)</f>
-        <v>66</v>
-      </c>
-      <c r="O20" s="12">
-        <f>ROUND(((O21*255)/31),0)</f>
-        <v>107</v>
-      </c>
-      <c r="P20" s="12">
-        <f>ROUND(((P21*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="R20" s="3">
-        <f>ROUND(((R21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <f>ROUND(((S21*255)/31),0)</f>
-        <v>90</v>
-      </c>
-      <c r="T20" s="3">
-        <f>ROUND(((T21*255)/31),0)</f>
-        <v>107</v>
-      </c>
-      <c r="V20" s="48">
-        <f>ROUND(((V21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W20" s="48">
-        <f>ROUND(((W21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="X20" s="48">
-        <f>ROUND(((X21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="48">
-        <f>ROUND(((Z21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="48">
-        <f>ROUND(((AA21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="48">
-        <f>ROUND(((AB21*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH20" s="29"/>
-      <c r="AI20" s="29"/>
-      <c r="AJ20" s="29"/>
-    </row>
-    <row r="21" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="5">
-        <v>12</v>
-      </c>
-      <c r="G21" s="5">
-        <v>25</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="5">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1">
-        <v>14</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O21" s="5">
-        <v>13</v>
-      </c>
-      <c r="P21" s="5">
-        <v>19</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="S21" s="1">
-        <v>11</v>
-      </c>
-      <c r="T21" s="1">
-        <v>13</v>
-      </c>
-      <c r="V21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="W21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="5"/>
-      <c r="AH21" s="5"/>
-    </row>
-    <row r="22" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="6">
-        <f>ROUND(((F24*255)/31),0)</f>
-        <v>247</v>
-      </c>
-      <c r="G23" s="6">
-        <f>ROUND(((G24*255)/31),0)</f>
-        <v>247</v>
-      </c>
-      <c r="H23" s="6">
-        <f>ROUND(((H24*255)/31),0)</f>
-        <v>33</v>
-      </c>
-      <c r="J23" s="7">
-        <f>ROUND(((J24*255)/31),0)</f>
-        <v>247</v>
-      </c>
-      <c r="K23" s="7">
-        <f>ROUND(((K24*255)/31),0)</f>
-        <v>140</v>
-      </c>
-      <c r="L23" s="7">
-        <f>ROUND(((L24*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="13">
-        <f>ROUND(((N24*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="O23" s="13">
-        <f>ROUND(((O24*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="P23" s="13">
-        <f>ROUND(((P24*255)/31),0)</f>
-        <v>25</v>
-      </c>
-      <c r="R23" s="14">
-        <f>ROUND(((R24*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="S23" s="14">
-        <f>ROUND(((S24*255)/31),0)</f>
-        <v>107</v>
-      </c>
-      <c r="T23" s="14">
-        <f>ROUND(((T24*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="49">
-        <f>ROUND(((V24*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="W23" s="49">
-        <f>ROUND(((W24*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="X23" s="49">
-        <f>ROUND(((X24*255)/31),0)</f>
-        <v>16</v>
-      </c>
-      <c r="Z23" s="58">
-        <f>ROUND(((Z24*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="AA23" s="58">
-        <f>ROUND(((AA24*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="AB23" s="58">
-        <f>ROUND(((AB24*255)/31),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AH23" s="29"/>
-      <c r="AI23" s="29"/>
-      <c r="AJ23" s="29"/>
-    </row>
-    <row r="24" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F24" s="5">
-        <v>30</v>
-      </c>
-      <c r="G24" s="5">
-        <v>30</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="1">
-        <v>30</v>
-      </c>
-      <c r="K24" s="1">
-        <v>17</v>
-      </c>
-      <c r="L24" s="5">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5">
-        <v>24</v>
-      </c>
-      <c r="O24" s="5">
-        <v>24</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="R24" s="1">
-        <v>24</v>
-      </c>
-      <c r="S24" s="1">
-        <v>13</v>
-      </c>
-      <c r="T24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="V24" s="5">
-        <v>18</v>
-      </c>
-      <c r="W24" s="5">
-        <v>18</v>
-      </c>
-      <c r="X24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" s="5">
-        <v>18</v>
-      </c>
-      <c r="AA24" s="5">
-        <v>10</v>
-      </c>
-      <c r="AB24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="5"/>
-      <c r="AF24" s="5"/>
-      <c r="AH24" s="5"/>
-      <c r="AI24" s="5"/>
-      <c r="AJ24" s="5"/>
-    </row>
-    <row r="25" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F26" s="4">
-        <f>ROUND(((F27*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="G26" s="4">
-        <f>ROUND(((G27*255)/31),0)</f>
-        <v>173</v>
-      </c>
-      <c r="H26" s="4">
-        <f>ROUND(((H27*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="J26" s="35">
-        <f>ROUND(((J27*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="K26" s="35">
-        <f>ROUND(((K27*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="L26" s="35">
-        <f>ROUND(((L27*255)/31),0)</f>
-        <v>255</v>
-      </c>
-      <c r="N26" s="38">
-        <f>ROUND(((N27*255)/31),0)</f>
-        <v>206</v>
-      </c>
-      <c r="O26" s="38">
-        <f>ROUND(((O27*255)/31),0)</f>
-        <v>140</v>
-      </c>
-      <c r="P26" s="38">
-        <f>ROUND(((P27*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="R26" s="41">
-        <f>ROUND(((R27*255)/31),0)</f>
-        <v>206</v>
-      </c>
-      <c r="S26" s="41">
-        <f>ROUND(((S27*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="T26" s="41">
-        <f>ROUND(((T27*255)/31),0)</f>
-        <v>206</v>
-      </c>
-      <c r="V26" s="50">
-        <f>ROUND(((V27*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="W26" s="50">
-        <f>ROUND(((W27*255)/31),0)</f>
-        <v>107</v>
-      </c>
-      <c r="X26" s="50">
-        <f>ROUND(((X27*255)/31),0)</f>
-        <v>115</v>
-      </c>
-      <c r="Z26" s="59">
-        <f>ROUND(((Z27*255)/31),0)</f>
-        <v>156</v>
-      </c>
-      <c r="AA26" s="59">
-        <f>ROUND(((AA27*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="AB26" s="59">
-        <f>ROUND(((AB27*255)/31),0)</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="5">
-        <v>31</v>
-      </c>
-      <c r="G27" s="5">
-        <v>21</v>
-      </c>
-      <c r="H27" s="5">
-        <v>24</v>
-      </c>
-      <c r="J27" s="5">
-        <v>31</v>
-      </c>
-      <c r="K27" s="5">
-        <v>15</v>
-      </c>
-      <c r="L27" s="5">
-        <v>31</v>
-      </c>
-      <c r="N27" s="5">
-        <v>25</v>
-      </c>
-      <c r="O27" s="5">
-        <v>17</v>
-      </c>
-      <c r="P27" s="5">
-        <v>19</v>
-      </c>
-      <c r="R27" s="5">
-        <v>25</v>
-      </c>
-      <c r="S27" s="5">
-        <v>12</v>
-      </c>
-      <c r="T27" s="5">
-        <v>25</v>
-      </c>
-      <c r="V27" s="5">
-        <v>19</v>
-      </c>
-      <c r="W27" s="5">
-        <v>13</v>
-      </c>
-      <c r="X27" s="5">
-        <v>14</v>
-      </c>
-      <c r="Z27" s="5">
-        <v>19</v>
-      </c>
-      <c r="AA27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB27" s="5">
-        <v>19</v>
-      </c>
-      <c r="AD27" s="5"/>
-      <c r="AE27" s="5"/>
-      <c r="AF27" s="5"/>
-      <c r="AH27" s="5"/>
-      <c r="AI27" s="5"/>
-      <c r="AJ27" s="5"/>
-    </row>
-    <row r="28" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F29" s="32">
-        <f>ROUND(((F30*255)/31),0)</f>
-        <v>181</v>
-      </c>
-      <c r="G29" s="32">
-        <f>ROUND(((G30*255)/31),0)</f>
-        <v>189</v>
-      </c>
-      <c r="H29" s="32">
-        <f>ROUND(((H30*255)/31),0)</f>
-        <v>197</v>
-      </c>
-      <c r="J29" s="31">
-        <f>ROUND(((J30*255)/31),0)</f>
-        <v>90</v>
-      </c>
-      <c r="K29" s="31">
-        <f>ROUND(((K30*255)/31),0)</f>
-        <v>107</v>
-      </c>
-      <c r="L29" s="31">
-        <f>ROUND(((L30*255)/31),0)</f>
-        <v>123</v>
-      </c>
-      <c r="N29" s="39">
-        <f>ROUND(((N30*255)/31),0)</f>
-        <v>132</v>
-      </c>
-      <c r="O29" s="39">
-        <f>ROUND(((O30*255)/31),0)</f>
-        <v>140</v>
-      </c>
-      <c r="P29" s="39">
-        <f>ROUND(((P30*255)/31),0)</f>
-        <v>148</v>
-      </c>
-      <c r="R29" s="40">
-        <f>ROUND(((R30*255)/31),0)</f>
-        <v>58</v>
-      </c>
-      <c r="S29" s="40">
-        <f>ROUND(((S30*255)/31),0)</f>
-        <v>66</v>
-      </c>
-      <c r="T29" s="40">
-        <f>ROUND(((T30*255)/31),0)</f>
-        <v>74</v>
-      </c>
-      <c r="V29" s="51">
-        <f>ROUND(((V30*255)/31),0)</f>
-        <v>82</v>
-      </c>
-      <c r="W29" s="51">
-        <f>ROUND(((W30*255)/31),0)</f>
-        <v>90</v>
-      </c>
-      <c r="X29" s="51">
-        <f>ROUND(((X30*255)/31),0)</f>
-        <v>99</v>
-      </c>
-      <c r="Z29" s="60">
-        <f>ROUND(((Z30*255)/31),0)</f>
-        <v>41</v>
-      </c>
-      <c r="AA29" s="60">
-        <f>ROUND(((AA30*255)/31),0)</f>
-        <v>49</v>
-      </c>
-      <c r="AB29" s="60">
-        <f>ROUND(((AB30*255)/31),0)</f>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F30" s="5">
-        <v>22</v>
-      </c>
-      <c r="G30" s="5">
-        <v>23</v>
-      </c>
-      <c r="H30" s="5">
-        <v>24</v>
-      </c>
-      <c r="J30" s="5">
-        <v>11</v>
-      </c>
-      <c r="K30" s="5">
-        <v>13</v>
-      </c>
-      <c r="L30" s="5">
-        <v>15</v>
-      </c>
-      <c r="N30" s="5">
-        <v>16</v>
-      </c>
-      <c r="O30" s="5">
-        <v>17</v>
-      </c>
-      <c r="P30" s="5">
-        <v>18</v>
-      </c>
-      <c r="R30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="T30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V30" s="5">
-        <v>10</v>
-      </c>
-      <c r="W30" s="5">
-        <v>11</v>
-      </c>
-      <c r="X30" s="5">
-        <v>12</v>
-      </c>
-      <c r="Z30" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD30" s="5"/>
-      <c r="AE30" s="5"/>
-      <c r="AF30" s="5"/>
-      <c r="AH30" s="5"/>
-      <c r="AI30" s="5"/>
-      <c r="AJ30" s="5"/>
-    </row>
-    <row r="31" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-    </row>
-    <row r="33" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="Z33" s="5"/>
-      <c r="AA33" s="5"/>
-      <c r="AB33" s="5"/>
-      <c r="AD33" s="5"/>
-      <c r="AE33" s="5"/>
-      <c r="AF33" s="5"/>
-      <c r="AH33" s="5"/>
-      <c r="AI33" s="5"/>
-      <c r="AJ33" s="5"/>
-    </row>
-    <row r="34" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-    </row>
-    <row r="35" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-    </row>
-    <row r="36" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-    </row>
-    <row r="37" spans="6:36" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="6:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D66BAD7-1404-4060-B374-C64959A2EF93}">
   <dimension ref="A1:AO38"/>
